--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484081_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484081_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3322</v>
+        <v>7.9787</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0221</v>
+        <v>4.6966</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3102</v>
+        <v>3.2821</v>
       </c>
       <c r="G2" t="n">
         <v>3.7251</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6784</v>
+        <v>1.3249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4535</v>
+        <v>1.128</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2249</v>
+        <v>0.1969</v>
       </c>
       <c r="V2" t="n">
         <v>1.7384</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5363</v>
+        <v>7.001</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2777</v>
+        <v>2.4056</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2587</v>
+        <v>4.5953</v>
       </c>
       <c r="G3" t="n">
         <v>2.0276</v>
@@ -688,13 +688,13 @@
         <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5464</v>
+        <v>0.9182</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2946</v>
+        <v>0.8333</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2518</v>
+        <v>0.0849</v>
       </c>
       <c r="V3" t="n">
         <v>1.2777</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0783</v>
+        <v>4.8774</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1516</v>
+        <v>2.2592</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9268</v>
+        <v>2.6182</v>
       </c>
       <c r="G4" t="n">
         <v>3.2011</v>
@@ -766,13 +766,13 @@
         <v>2.9758</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8177</v>
+        <v>1.6168</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1791</v>
+        <v>1.2868</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3373</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0686</v>
+        <v>0.4978</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7841</v>
+        <v>-2.1865</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8527</v>
+        <v>2.6844</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8285</v>
@@ -844,13 +844,13 @@
         <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3534</v>
+        <v>1.7826</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7346</v>
+        <v>1.3321</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6188</v>
+        <v>0.4505</v>
       </c>
       <c r="V5" t="n">
         <v>0.9405</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1377</v>
+        <v>-0.2948</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.7357</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8337</v>
+        <v>0.441</v>
       </c>
       <c r="G6" t="n">
         <v>-1.751</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0078</v>
+        <v>0.5753</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3288</v>
+        <v>0.2891</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="V6" t="n">
         <v>1.2777</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5337</v>
+        <v>-0.3908</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.338</v>
+        <v>4.1787</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8043</v>
+        <v>-4.5695</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8667</v>
+        <v>1.6314</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1102</v>
+        <v>3.1149</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-1.4834</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.76</v>
+        <v>2.4151</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1199</v>
+        <v>3.7755</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.64</v>
+        <v>-1.3604</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1068</v>
+        <v>-0.7837</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0098</v>
+        <v>-0.6607</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1165</v>
+        <v>-0.123</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.865</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6122</v>
+        <v>0.4138</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2527</v>
+        <v>-0.3486</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.532</v>
+        <v>-2.4842</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.3417</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.532</v>
+        <v>-4.8259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6317</v>
+        <v>-0.574</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2184</v>
+        <v>-1.4344</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.8501</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6314</v>
+        <v>-0.8667</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1149</v>
+        <v>-0.1102</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4834</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4151</v>
+        <v>-0.76</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7755</v>
+        <v>-0.1199</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3604</v>
+        <v>-0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7837</v>
+        <v>-0.1068</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6607</v>
+        <v>0.0098</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.123</v>
+        <v>-0.1165</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1757</v>
+        <v>0.8247</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4535</v>
+        <v>0.5159</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6292</v>
+        <v>0.3089</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4842</v>
+        <v>-0.532</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3417</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.8259</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3493</v>
+        <v>-1.8553</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7229</v>
+        <v>-0.9578</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3736</v>
+        <v>-0.8975</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9762</v>
+        <v>-1.5463</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.4281</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.893</v>
+        <v>-1.9744</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5464</v>
+        <v>-0.9117</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7742</v>
+        <v>0.4085</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3207</v>
+        <v>-1.3202</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4298</v>
+        <v>-0.6347</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4276</v>
+        <v>-0.6542</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3806</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1507</v>
+        <v>-0.1105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2041</v>
+        <v>-0.0623</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0534</v>
+        <v>-0.0483</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0713</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. MORRO BALERA</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6501</v>
+        <v>-1.8624</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7968</v>
+        <v>-3.2921</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8532999999999999</v>
+        <v>1.4297</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3425</v>
+        <v>-1.9762</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1312</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2113</v>
+        <v>-2.893</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6802</v>
+        <v>-1.5464</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.7742</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6802</v>
+        <v>-3.3207</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6623</v>
+        <v>-0.4298</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1312</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5312</v>
+        <v>0.4276</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-2.3806</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5141</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1247</v>
+        <v>0.6349</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3894</v>
+        <v>0.0027</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>H. MORRO BALERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8014</v>
+        <v>-2.6221</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-1.7968</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.815</v>
+        <v>-0.8253</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6589</v>
+        <v>-1.3425</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.305</v>
+        <v>-0.1312</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3539</v>
+        <v>-1.2113</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2719</v>
+        <v>-0.6802</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9115</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3604</v>
+        <v>-0.6802</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.387</v>
+        <v>-0.6623</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3935</v>
+        <v>-0.1312</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0065</v>
+        <v>-0.5312</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1352</v>
+        <v>-0.486</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8762</v>
+        <v>-0.1247</v>
       </c>
       <c r="U11" t="n">
-        <v>0.259</v>
+        <v>-0.3614</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.881</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8852</v>
+        <v>-3.5833</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8194</v>
+        <v>-1.7403</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0658</v>
+        <v>-1.843</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5463</v>
+        <v>-2.6589</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4281</v>
+        <v>-1.305</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9744</v>
+        <v>-1.3539</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9117</v>
+        <v>-2.2719</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4085</v>
+        <v>-0.9115</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3202</v>
+        <v>-1.3604</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6347</v>
+        <v>-0.387</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0195</v>
+        <v>-0.3935</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6542</v>
+        <v>0.0065</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1903</v>
+        <v>-1.3887</v>
       </c>
       <c r="R12" t="n">
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1404</v>
+        <v>1.3533</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9238</v>
+        <v>1.1224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2166</v>
+        <v>0.2309</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.301700000000001</v>
+        <v>9.172200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4739</v>
+        <v>1.3965</v>
       </c>
       <c r="F13" t="n">
-        <v>7.775800000000001</v>
+        <v>7.7758</v>
       </c>
       <c r="G13" t="n">
         <v>-1.384900000000001</v>
@@ -1441,7 +1441,7 @@
         <v>-10.7856</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2652000000000003</v>
+        <v>0.2651999999999997</v>
       </c>
       <c r="K13" t="n">
         <v>11.926</v>
@@ -1456,7 +1456,7 @@
         <v>-2.5256</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8752999999999996</v>
+        <v>0.8752999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.9838</v>
@@ -1468,13 +1468,13 @@
         <v>17.8547</v>
       </c>
       <c r="S13" t="n">
-        <v>6.631600000000001</v>
+        <v>8.5021</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4989</v>
+        <v>7.3693</v>
       </c>
       <c r="U13" t="n">
-        <v>1.132500000000001</v>
+        <v>1.1327</v>
       </c>
       <c r="V13" t="n">
         <v>0.07109999999999994</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2047</v>
+        <v>3.5458</v>
       </c>
       <c r="E14" t="n">
-        <v>1.988</v>
+        <v>1.4779</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2167</v>
+        <v>2.0679</v>
       </c>
       <c r="G14" t="n">
         <v>1.178</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5639999999999999</v>
+        <v>-0.0949</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2495</v>
+        <v>-0.2606</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3145</v>
+        <v>0.1657</v>
       </c>
       <c r="V14" t="n">
         <v>0.6773</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0879</v>
+        <v>2.2365</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5624</v>
+        <v>2.3787</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4746</v>
+        <v>-0.1421</v>
       </c>
       <c r="G15" t="n">
         <v>1.7367</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8756</v>
+        <v>-0.727</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.1813</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8781</v>
+        <v>-0.5457</v>
       </c>
       <c r="V15" t="n">
         <v>0.4332</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8358</v>
+        <v>0.6836</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4047</v>
+        <v>0.2007</v>
       </c>
       <c r="F16" t="n">
-        <v>0.431</v>
+        <v>0.4829</v>
       </c>
       <c r="G16" t="n">
         <v>0.8509</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4653</v>
+        <v>0.3132</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2438</v>
+        <v>0.0397</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2216</v>
+        <v>0.2734</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4724</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9777</v>
+        <v>0.229</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7799</v>
+        <v>0.8912</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8022</v>
+        <v>-0.6623</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.266</v>
+        <v>-1.8275</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0656</v>
+        <v>-4.4199</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7996</v>
+        <v>2.5924</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.11</v>
+        <v>-1.4319</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2706</v>
+        <v>-1.9642</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1606</v>
+        <v>0.5323</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.156</v>
+        <v>-0.3956</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.795</v>
+        <v>-2.4557</v>
       </c>
       <c r="O17" t="n">
-        <v>1.639</v>
+        <v>2.0601</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9758</v>
+        <v>0.9919</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.9596</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>2.9758</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3354</v>
+        <v>-1.3731</v>
       </c>
       <c r="T17" t="n">
-        <v>3.095</v>
+        <v>-0.4476</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.9255</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0713</v>
+        <v>2.4376</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1947</v>
+        <v>4.7546</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-2.317</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0396</v>
+        <v>-1.2019</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9889</v>
+        <v>-1.0909</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0507</v>
+        <v>-0.111</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3131</v>
@@ -1858,13 +1858,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2273</v>
+        <v>-0.3897</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.255</v>
+        <v>-0.357</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0277</v>
+        <v>-0.0327</v>
       </c>
       <c r="V18" t="n">
         <v>0.6992</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>D. CORTES ALEJANDRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4877</v>
+        <v>-1.2591</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3331</v>
+        <v>-0.9029</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1545</v>
+        <v>-0.3562</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8275</v>
+        <v>-1.7158</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.4199</v>
+        <v>-1.0887</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5924</v>
+        <v>-0.627</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4319</v>
+        <v>-0.6698</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9642</v>
+        <v>0.6505</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5323</v>
+        <v>-1.3202</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3956</v>
+        <v>-1.046</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4557</v>
+        <v>-1.7392</v>
       </c>
       <c r="O19" t="n">
-        <v>2.0601</v>
+        <v>0.6932</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9758</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.0897</v>
+        <v>-1.0259</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.672</v>
+        <v>-0.4477</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4178</v>
+        <v>-0.5782</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4376</v>
+        <v>1.0858</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7546</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.317</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CORTES ALEJANDRE</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6332</v>
+        <v>-1.2901</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.005</v>
+        <v>-0.51</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6282</v>
+        <v>-0.7801</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7158</v>
+        <v>-0.0945</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0887</v>
+        <v>-0.101</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.627</v>
+        <v>0.0065</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6698</v>
+        <v>0.3629</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6505</v>
+        <v>0.3629</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3202</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.046</v>
+        <v>-0.4574</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7392</v>
+        <v>-0.4639</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6932</v>
+        <v>0.0065</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4</v>
+        <v>0.0028</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5498</v>
+        <v>0.1191</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.1162</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0858</v>
+        <v>-0.6032</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1206</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6523</v>
+        <v>-1.4373</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.9574</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0945</v>
+        <v>0.5585</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.101</v>
+        <v>0.2969</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0065</v>
+        <v>0.2616</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3629</v>
+        <v>0.2555</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3629</v>
+        <v>1.0887</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4574</v>
+        <v>0.303</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4639</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0065</v>
+        <v>1.0948</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3594</v>
+        <v>-0.5073</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.187</v>
+        <v>-0.221</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1723</v>
+        <v>-0.2863</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6032</v>
+        <v>-2.6789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6032</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8879</v>
+        <v>-3.0863</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-4.0245</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0326</v>
+        <v>0.9382</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5585</v>
+        <v>-0.266</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2969</v>
+        <v>-2.0656</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2616</v>
+        <v>1.7996</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2555</v>
+        <v>-0.11</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0887</v>
+        <v>-0.2706</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.1606</v>
       </c>
       <c r="M22" t="n">
-        <v>0.303</v>
+        <v>-0.156</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-1.795</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0948</v>
+        <v>1.639</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-4.9596</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9579</v>
+        <v>0.2268</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1189</v>
+        <v>0.8504</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8389</v>
+        <v>-0.6236</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6789</v>
+        <v>-0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6789</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7519</v>
+        <v>-3.6814</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7463</v>
+        <v>-4.0321</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0056</v>
+        <v>0.3507</v>
       </c>
       <c r="G23" t="n">
         <v>2.2776</v>
@@ -2248,13 +2248,13 @@
         <v>2.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0865</v>
+        <v>-1.016</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9408</v>
+        <v>-0.2266</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1457</v>
+        <v>-0.7894</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5785</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3019</v>
+        <v>-5.261200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.5694</v>
+        <v>-6.5693</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7325000000000002</v>
+        <v>1.308</v>
       </c>
       <c r="G24" t="n">
         <v>1.3848</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.400599999999999</v>
+        <v>-9.400600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>10.7856</v>
@@ -2305,10 +2305,10 @@
         <v>2.5254</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8752999999999999</v>
+        <v>-0.8753000000000003</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2651000000000003</v>
+        <v>-0.2650999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-11.926</v>
@@ -2326,16 +2326,16 @@
         <v>15.8707</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.631699999999999</v>
+        <v>-4.5911</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1327</v>
+        <v>-1.1326</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.4989</v>
+        <v>-3.4585</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.07119999999999971</v>
+        <v>-0.07119999999999937</v>
       </c>
       <c r="W24" t="n">
         <v>10.7678</v>
